--- a/docs/specs/whereisit-table-spec-v2.xlsx
+++ b/docs/specs/whereisit-table-spec-v2.xlsx
@@ -93,7 +93,7 @@
     <t>API 예약 컬럼</t>
   </si>
   <si>
-    <t>습득 장소·보관기관 연락처·상세 설명은 원본에서 상세 API 매핑 확인 전으로 둔 NULL 허용 컬럼입니다. 새로 검증한 값이 아닙니다.</t>
+    <t>습득 장소(fdPlace)·보관기관 연락처(tel)·상세 설명(uniq)은 일반·포털 상세 API에서 제공됩니다. 상세 호출 실패·미실행 또는 필드 누락 가능성 때문에 NULL 허용을 유지합니다.</t>
   </si>
   <si>
     <t>관계 주의</t>
@@ -1245,7 +1245,7 @@
     <t>확정된 수신 이메일</t>
   </si>
   <si>
-    <t>습득 장소: 상세 API 매핑 확인 후 저장</t>
+    <t>fdPlace → found_place: 일반·포털 상세 API 제공; 상세조회 성공 시 저장; NULL 허용</t>
   </si>
   <si>
     <t>보관기관_연락처</t>
@@ -1263,7 +1263,7 @@
     <t>메일_제목</t>
   </si>
   <si>
-    <t>보관기관 연락처: 상세 매핑 확인 후 저장</t>
+    <t>tel → storage_phone: 일반·포털 상세 API 제공; 상세조회 성공 시 저장; NULL 허용</t>
   </si>
   <si>
     <t>상세_설명</t>
@@ -1278,7 +1278,7 @@
     <t>body</t>
   </si>
   <si>
-    <t>상세설명: 상세 API 매핑 확인 후 저장</t>
+    <t>uniq → description: 특이사항 또는 상세 텍스트; 일반·포털 상세 API 제공; 상세조회 성공 시 저장; NULL 허용</t>
   </si>
   <si>
     <t>상세_조회_시각</t>
@@ -1344,7 +1344,7 @@
     <t>VARCHAR(64)</t>
   </si>
   <si>
-    <t>일반·포털기관 API 원본을 출처별 외부 식별자로 구분합니다. 상세 API 확인 전 예약 컬럼은 원본과 같이 NULL 허용입니다.</t>
+    <t>일반·포털기관 API 원본을 (source_type, atc_id, fd_sn) 외부 중복 식별자로 구분합니다. 상세조회 필드 매핑은 확인됐지만 상세 호출 실패·미실행 또는 필드 누락 가능성 때문에 상세 컬럼은 선택(NULL 허용)으로 유지합니다.</t>
   </si>
   <si>
     <t>민감정보를 제외한 발송 오류 코드</t>
@@ -1485,13 +1485,13 @@
     <t>로그인할 때마다 한 행을 추가합니다(기기별 세션). refresh하면 쓴 행을 지우고 새 행을 넣고(회전), 로그아웃하면 그 행을 지웁니다. 만료된 행은 로그인·refresh 때 해당 회원 것을 지웁니다. 원문 토큰은 저장하지 않습니다.</t>
   </si>
   <si>
-    <t>어디갔지 | 테이블 명세서 v2</t>
-  </si>
-  <si>
-    <t>v2 · 한글 논리명 + 영문 물리명 · MySQL 구현 기준</t>
-  </si>
-  <si>
-    <t>간소화안 v0.3과 회원 도메인(API 명세 v2)을 반영 · 2026-09-24 · 실제 MySQL / ERDCloud 실행 미검증</t>
+    <t>어디갔지 | 테이블 명세서 v2.1</t>
+  </si>
+  <si>
+    <t>v2.1 · 한글 논리명 + 영문 물리명 · MySQL 구현 기준</t>
+  </si>
+  <si>
+    <t>간소화안 v0.3과 회원 도메인(API 명세 v2.1)을 반영 · 2026-09-26 · 실제 MySQL / ERDCloud 실행 미검증</t>
   </si>
   <si>
     <t>업무 용어와 ERD는 한글 논리명을 사용하고, 실제 MySQL CREATE TABLE·컬럼·키·제약조건·인덱스는 소문자 영문 snake_case 물리명을 사용합니다.</t>

--- a/docs/specs/whereisit-table-spec-v2.xlsx
+++ b/docs/specs/whereisit-table-spec-v2.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="586">
   <si>
     <t>어디갔지 | 한글 테이블 명세서</t>
   </si>
@@ -1747,6 +1747,39 @@
   </si>
   <si>
     <t>기준: v2 신규(회원 도메인, API 명세 v2) | 한글은 논리명·설명, 영문 이름은 MySQL 물리명. 실제 DB 실행 미검증.</t>
+  </si>
+  <si>
+    <t>물품명_검색어</t>
+  </si>
+  <si>
+    <t>product_name_keyword</t>
+  </si>
+  <si>
+    <t>API-05에서 AI가 구조화한 포털기관 물품명 검색어(PRDT_NM). 추적 재검색 매칭과 API-16 물품 종류 표시값(itemTypeName)에 사용</t>
+  </si>
+  <si>
+    <t>Issue #85 Entity로 추가(기준 SQL 이후). Issue #99 API-16 itemTypeName</t>
+  </si>
+  <si>
+    <t>보관장소_검색어</t>
+  </si>
+  <si>
+    <t>storage_place_keyword</t>
+  </si>
+  <si>
+    <t>API-05에서 AI가 구조화한 포털기관 보관장소 검색어(DEP_PLACE). 분실 장소(lost_place_text)와 다름</t>
+  </si>
+  <si>
+    <t>Issue #85 Entity로 추가(기준 SQL 이후)</t>
+  </si>
+  <si>
+    <t>표시_색상명</t>
+  </si>
+  <si>
+    <t>사용자가 등록한 분실물의 표시용 색상명(예: 검정). API-05에서 AI가 사용자가 명시한 색상만 저장하고 없거나 모호하면 NULL. 공식 color_code와 다르며 API-16 colorName으로 표시</t>
+  </si>
+  <si>
+    <t>Issue #99 Entity로 추가(Migration 없음). 기존 행 backfill 없음</t>
   </si>
 </sst>
 </file>
@@ -2263,7 +2296,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A6:K26" displayName="Schema_lost_items" name="Schema_lost_items" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A6:K29" displayName="Schema_lost_items" name="Schema_lost_items" id="6">
   <tableColumns count="11">
     <tableColumn name="순번" id="1"/>
     <tableColumn name="한글 논리 컬럼명" id="2"/>
@@ -2586,7 +2619,7 @@
       </c>
       <c r="C6" s="6">
         <f>SUM('01_테이블목록'!E7:E13)</f>
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E6" s="6">
         <f>COUNTA('02_관계'!B7:B13)</f>
@@ -8602,8 +8635,8 @@
         <v>90</v>
       </c>
       <c r="E8" s="21">
-        <f>COUNT('06_분실물검색추적'!A7:A26)</f>
-        <v>20</v>
+        <f>COUNT('06_분실물검색추적'!A7:A29)</f>
+        <v>23</v>
       </c>
       <c r="F8" s="19" t="s">
         <v>265</v>
@@ -16847,35 +16880,109 @@
         <v>287</v>
       </c>
     </row>
-    <row r="27" ht="30.0" customHeight="1">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-    </row>
-    <row r="28" ht="30.0" customHeight="1">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-    </row>
-    <row r="29" ht="37.5" customHeight="1">
-      <c r="A29" s="14" t="s">
-        <v>379</v>
+    <row r="27" ht="45.0" customHeight="1">
+      <c r="A27" s="20">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>576</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>367</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="H27" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="I27" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="J27" s="18" t="s">
+        <v>577</v>
+      </c>
+      <c r="K27" s="18" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="28" ht="45.0" customHeight="1">
+      <c r="A28" s="21">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>579</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>580</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="H28" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="I28" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="J28" s="19" t="s">
+        <v>581</v>
+      </c>
+      <c r="K28" s="19" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="29" ht="45.0" customHeight="1">
+      <c r="A29" s="20">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>583</v>
+      </c>
+      <c r="C29" s="31" t="s">
+        <v>381</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>377</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="G29" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="H29" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="I29" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="J29" s="18" t="s">
+        <v>584</v>
+      </c>
+      <c r="K29" s="18" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="30" ht="30.0" customHeight="1">
@@ -16904,18 +17011,10 @@
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
     </row>
-    <row r="32" ht="30.0" customHeight="1">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
+    <row r="32" ht="37.5" customHeight="1">
+      <c r="A32" s="14" t="s">
+        <v>379</v>
+      </c>
     </row>
     <row r="33" ht="30.0" customHeight="1">
       <c r="A33" s="4"/>
@@ -17963,7 +18062,7 @@
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="A32:K32"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
